--- a/tableau-synthese.xlsx
+++ b/tableau-synthese.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="49">
   <si>
     <t xml:space="preserve">BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">07/10/2024-21/10/2024</t>
   </si>
   <si>
-    <t xml:space="preserve">API ( filezilla )</t>
+    <t xml:space="preserve">Serveur FTP ( API )</t>
   </si>
   <si>
     <t xml:space="preserve">21/03/2025-11/04/2025</t>
@@ -205,6 +205,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -226,12 +227,14 @@
       <sz val="20"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="18"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -239,6 +242,7 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -246,72 +250,85 @@
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="14"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="15"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="36"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="15"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="15"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="15"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1261,7 +1278,9 @@
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
+      <c r="E15" s="21" t="s">
+        <v>26</v>
+      </c>
       <c r="F15" s="21"/>
       <c r="G15" s="21"/>
       <c r="H15" s="22" t="s">
@@ -1293,7 +1312,9 @@
       <c r="B17" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="21"/>
+      <c r="C17" s="21" t="s">
+        <v>26</v>
+      </c>
       <c r="D17" s="21"/>
       <c r="E17" s="21" t="s">
         <v>26</v>
